--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 60 D100 Spring 2024 24GE03I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 60 D100 Spring 2024 24GE03I33 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Zooplankton Counts\Erie\Spring 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E5A615-629B-4577-89B5-FDFA1F689FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CAD3C3-A8AD-45DE-B7EA-A29E97F2B5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{1A6D3390-7485-42D1-9462-B8FC2164D4A9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1A6D3390-7485-42D1-9462-B8FC2164D4A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="14021" r:id="rId2"/>
+    <pivotCache cacheId="39" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -523,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -541,7 +541,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -5405,7 +5404,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB625187-15D7-4716-94D9-499DB9D6CDE9}" name="PivotTable10" cacheId="14021" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB625187-15D7-4716-94D9-499DB9D6CDE9}" name="PivotTable10" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="S3:V27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5879,21 +5878,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB8D8C8-861C-4C7D-AE0F-98369D6D1283}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:V238"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="18" max="18" width="43.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.88671875" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="18" max="18" width="43.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6181,17 +6181,17 @@
       <c r="S5" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="T5" s="11">
+      <c r="T5">
         <v>0</v>
       </c>
-      <c r="U5" s="11">
-        <v>1</v>
-      </c>
-      <c r="V5" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6246,17 +6246,17 @@
       <c r="S6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T6" s="11">
+      <c r="T6">
         <v>8</v>
       </c>
-      <c r="U6" s="11">
+      <c r="U6">
         <v>5</v>
       </c>
-      <c r="V6" s="11">
+      <c r="V6">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6311,17 +6311,17 @@
       <c r="S7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="T7" s="11">
-        <v>2</v>
-      </c>
-      <c r="U7" s="11">
-        <v>1</v>
-      </c>
-      <c r="V7" s="11">
+      <c r="T7">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6376,17 +6376,17 @@
       <c r="S8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="T8" s="11">
-        <v>23</v>
-      </c>
-      <c r="U8" s="11">
+      <c r="T8">
+        <v>23</v>
+      </c>
+      <c r="U8">
         <v>40</v>
       </c>
-      <c r="V8" s="11">
+      <c r="V8">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6441,17 +6441,17 @@
       <c r="S9" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T9" s="11">
-        <v>1</v>
-      </c>
-      <c r="U9" s="11">
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
         <v>4</v>
       </c>
-      <c r="V9" s="11">
+      <c r="V9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6506,17 +6506,17 @@
       <c r="S10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T10" s="11">
-        <v>2</v>
-      </c>
-      <c r="U10" s="11">
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6571,17 +6571,17 @@
       <c r="S11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T11" s="11">
+      <c r="T11">
         <v>21</v>
       </c>
-      <c r="U11" s="11">
+      <c r="U11">
         <v>29</v>
       </c>
-      <c r="V11" s="11">
+      <c r="V11">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6636,17 +6636,17 @@
       <c r="S12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="T12" s="11">
+      <c r="T12">
         <v>12</v>
       </c>
-      <c r="U12" s="11">
+      <c r="U12">
         <v>11</v>
       </c>
-      <c r="V12" s="11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6704,17 +6704,17 @@
       <c r="S13" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="T13" s="11">
+      <c r="T13">
         <v>0</v>
       </c>
-      <c r="U13" s="11">
-        <v>1</v>
-      </c>
-      <c r="V13" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6769,17 +6769,17 @@
       <c r="S14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="T14" s="11">
+      <c r="T14">
         <v>0</v>
       </c>
-      <c r="U14" s="11">
-        <v>1</v>
-      </c>
-      <c r="V14" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6834,17 +6834,17 @@
       <c r="S15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="T15" s="11">
+      <c r="T15">
         <v>9</v>
       </c>
-      <c r="U15" s="11">
+      <c r="U15">
         <v>8</v>
       </c>
-      <c r="V15" s="11">
+      <c r="V15">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6902,17 +6902,17 @@
       <c r="S16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T16" s="11">
+      <c r="T16">
         <v>47</v>
       </c>
-      <c r="U16" s="11">
+      <c r="U16">
         <v>47</v>
       </c>
-      <c r="V16" s="11">
+      <c r="V16">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -6967,17 +6967,17 @@
       <c r="S17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T17" s="11">
+      <c r="T17">
         <v>44</v>
       </c>
-      <c r="U17" s="11">
+      <c r="U17">
         <v>55</v>
       </c>
-      <c r="V17" s="11">
+      <c r="V17">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7035,17 +7035,17 @@
       <c r="S18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="T18" s="11">
+      <c r="T18">
         <v>57</v>
       </c>
-      <c r="U18" s="11">
+      <c r="U18">
         <v>60</v>
       </c>
-      <c r="V18" s="11">
+      <c r="V18">
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7100,17 +7100,17 @@
       <c r="S19" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="T19" s="11">
-        <v>1</v>
-      </c>
-      <c r="U19" s="11">
-        <v>2</v>
-      </c>
-      <c r="V19" s="11">
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>2</v>
+      </c>
+      <c r="V19">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7165,17 +7165,17 @@
       <c r="S20" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T20" s="11">
+      <c r="T20">
         <v>4</v>
       </c>
-      <c r="U20" s="11">
+      <c r="U20">
         <v>0</v>
       </c>
-      <c r="V20" s="11">
+      <c r="V20">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7230,17 +7230,17 @@
       <c r="S21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T21" s="11">
-        <v>1</v>
-      </c>
-      <c r="U21" s="11">
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
         <v>0</v>
       </c>
-      <c r="V21" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7295,17 +7295,17 @@
       <c r="S22" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="T22" s="11">
-        <v>1</v>
-      </c>
-      <c r="U22" s="11">
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
         <v>6</v>
       </c>
-      <c r="V22" s="11">
+      <c r="V22">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7360,17 +7360,17 @@
       <c r="S23" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="T23" s="11">
-        <v>1</v>
-      </c>
-      <c r="U23" s="11">
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23">
         <v>0</v>
       </c>
-      <c r="V23" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7425,17 +7425,17 @@
       <c r="S24" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="T24" s="11">
-        <v>1</v>
-      </c>
-      <c r="U24" s="11">
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7490,17 +7490,17 @@
       <c r="S25" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="T25" s="11">
+      <c r="T25">
         <v>0</v>
       </c>
-      <c r="U25" s="11">
-        <v>1</v>
-      </c>
-      <c r="V25" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U25">
+        <v>1</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7555,17 +7555,17 @@
       <c r="S26" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="T26" s="11">
+      <c r="T26">
         <v>0</v>
       </c>
-      <c r="U26" s="11">
-        <v>1</v>
-      </c>
-      <c r="V26" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U26">
+        <v>1</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7620,17 +7620,17 @@
       <c r="S27" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="T27" s="11">
+      <c r="T27">
         <v>235</v>
       </c>
-      <c r="U27" s="11">
+      <c r="U27">
         <v>273</v>
       </c>
-      <c r="V27" s="11">
+      <c r="V27">
         <v>508</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7738,13 +7738,13 @@
       <c r="R29" t="s">
         <v>47</v>
       </c>
-      <c r="S29" s="12" t="s">
+      <c r="S29" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+    </row>
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7796,17 +7796,17 @@
       <c r="Q30">
         <v>1</v>
       </c>
-      <c r="S30" s="12" t="s">
+      <c r="S30" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="T30" s="14" t="s">
+      <c r="T30" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="U30" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U30" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7858,15 +7858,15 @@
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="S31" s="12"/>
-      <c r="T31" s="14" t="s">
+      <c r="S31" s="11"/>
+      <c r="T31" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="U31" s="13">
+      <c r="U31" s="12">
         <v>0.998</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7918,17 +7918,17 @@
       <c r="Q32">
         <v>1</v>
       </c>
-      <c r="S32" s="12" t="s">
+      <c r="S32" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="T32" s="14" t="s">
+      <c r="T32" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="U32" s="13">
+      <c r="U32" s="12">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7980,15 +7980,15 @@
       <c r="Q33">
         <v>1</v>
       </c>
-      <c r="S33" s="13"/>
-      <c r="T33" s="14" t="s">
+      <c r="S33" s="12"/>
+      <c r="T33" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="U33" s="13">
+      <c r="U33" s="12">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8040,15 +8040,15 @@
       <c r="Q34">
         <v>1</v>
       </c>
-      <c r="S34" s="12" t="s">
+      <c r="S34" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="T34" s="14" t="s">
+      <c r="T34" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="U34" s="15"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U34" s="14"/>
+    </row>
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8100,15 +8100,15 @@
       <c r="Q35">
         <v>1</v>
       </c>
-      <c r="S35" s="12" t="s">
+      <c r="S35" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="T35" s="13" t="s">
+      <c r="T35" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="U35" s="13"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U35" s="12"/>
+    </row>
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8160,14 +8160,14 @@
       <c r="Q36">
         <v>1</v>
       </c>
-      <c r="S36" s="12" t="s">
+      <c r="S36" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="13"/>
-      <c r="U36" s="13"/>
-      <c r="V36" s="13"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T36" s="12"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+    </row>
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11197,7 +11197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12260,7 +12260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13541,7 +13541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14177,7 +14177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14230,7 +14230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14551,7 +14551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14816,7 +14816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15293,7 +15293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15558,7 +15558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15667,7 +15667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15826,7 +15826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15932,7 +15932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16041,7 +16041,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16256,7 +16256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16362,7 +16362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16468,7 +16468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16521,7 +16521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16630,7 +16630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16683,7 +16683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16736,7 +16736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17060,7 +17060,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17166,7 +17166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17219,7 +17219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17431,7 +17431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17537,7 +17537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17802,7 +17802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17858,7 +17858,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18335,7 +18335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="5" t="s">
         <v>18</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="5" t="s">
         <v>18</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="5" t="s">
         <v>18</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="5" t="s">
         <v>18</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="5" t="s">
         <v>18</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="5" t="s">
         <v>18</v>
       </c>
@@ -18706,7 +18706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="5" t="s">
         <v>18</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="5" t="s">
         <v>18</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="5" t="s">
         <v>18</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="5" t="s">
         <v>18</v>
       </c>
@@ -18919,6 +18919,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V238" xr:uid="{DCB8D8C8-861C-4C7D-AE0F-98369D6D1283}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Harpacticoida spp."/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/raw/GLNPO 2024 Spring/Erie/D100/ER 60 D100 Spring 2024 24GE03I33 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D100/ER 60 D100 Spring 2024 24GE03I33 Zoop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GL Lab User\Desktop\GLNPO Zooplankton Counts\Erie\Spring 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CAD3C3-A8AD-45DE-B7EA-A29E97F2B5E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E5A615-629B-4577-89B5-FDFA1F689FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1A6D3390-7485-42D1-9462-B8FC2164D4A9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{1A6D3390-7485-42D1-9462-B8FC2164D4A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="39" r:id="rId2"/>
+    <pivotCache cacheId="14021" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -523,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -541,6 +541,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -5404,7 +5405,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB625187-15D7-4716-94D9-499DB9D6CDE9}" name="PivotTable10" cacheId="39" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB625187-15D7-4716-94D9-499DB9D6CDE9}" name="PivotTable10" cacheId="14021" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="S3:V27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -5878,22 +5879,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB8D8C8-861C-4C7D-AE0F-98369D6D1283}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:V238"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.88671875" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" customWidth="1"/>
-    <col min="18" max="18" width="43.44140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" customWidth="1"/>
+    <col min="18" max="18" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6181,17 +6181,17 @@
       <c r="S5" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="11">
         <v>0</v>
       </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U5" s="11">
+        <v>1</v>
+      </c>
+      <c r="V5" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6246,17 +6246,17 @@
       <c r="S6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="11">
         <v>8</v>
       </c>
-      <c r="U6">
+      <c r="U6" s="11">
         <v>5</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="11">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6311,17 +6311,17 @@
       <c r="S7" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
+      <c r="T7" s="11">
+        <v>2</v>
+      </c>
+      <c r="U7" s="11">
+        <v>1</v>
+      </c>
+      <c r="V7" s="11">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6376,17 +6376,17 @@
       <c r="S8" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="T8">
-        <v>23</v>
-      </c>
-      <c r="U8">
+      <c r="T8" s="11">
+        <v>23</v>
+      </c>
+      <c r="U8" s="11">
         <v>40</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="11">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6441,17 +6441,17 @@
       <c r="S9" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
+      <c r="T9" s="11">
+        <v>1</v>
+      </c>
+      <c r="U9" s="11">
         <v>4</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6506,17 +6506,17 @@
       <c r="S10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
-      <c r="U10">
+      <c r="T10" s="11">
+        <v>2</v>
+      </c>
+      <c r="U10" s="11">
         <v>0</v>
       </c>
-      <c r="V10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V10" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6571,17 +6571,17 @@
       <c r="S11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="11">
         <v>21</v>
       </c>
-      <c r="U11">
+      <c r="U11" s="11">
         <v>29</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="11">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6636,17 +6636,17 @@
       <c r="S12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="11">
         <v>12</v>
       </c>
-      <c r="U12">
+      <c r="U12" s="11">
         <v>11</v>
       </c>
-      <c r="V12">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V12" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6704,17 +6704,17 @@
       <c r="S13" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="11">
         <v>0</v>
       </c>
-      <c r="U13">
-        <v>1</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U13" s="11">
+        <v>1</v>
+      </c>
+      <c r="V13" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6769,17 +6769,17 @@
       <c r="S14" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="T14">
+      <c r="T14" s="11">
         <v>0</v>
       </c>
-      <c r="U14">
-        <v>1</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U14" s="11">
+        <v>1</v>
+      </c>
+      <c r="V14" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -6834,17 +6834,17 @@
       <c r="S15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="T15">
+      <c r="T15" s="11">
         <v>9</v>
       </c>
-      <c r="U15">
+      <c r="U15" s="11">
         <v>8</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="11">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6902,17 +6902,17 @@
       <c r="S16" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="T16">
+      <c r="T16" s="11">
         <v>47</v>
       </c>
-      <c r="U16">
+      <c r="U16" s="11">
         <v>47</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="11">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -6967,17 +6967,17 @@
       <c r="S17" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="11">
         <v>44</v>
       </c>
-      <c r="U17">
+      <c r="U17" s="11">
         <v>55</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="11">
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7035,17 +7035,17 @@
       <c r="S18" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="11">
         <v>57</v>
       </c>
-      <c r="U18">
+      <c r="U18" s="11">
         <v>60</v>
       </c>
-      <c r="V18">
+      <c r="V18" s="11">
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7100,17 +7100,17 @@
       <c r="S19" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-      <c r="U19">
-        <v>2</v>
-      </c>
-      <c r="V19">
+      <c r="T19" s="11">
+        <v>1</v>
+      </c>
+      <c r="U19" s="11">
+        <v>2</v>
+      </c>
+      <c r="V19" s="11">
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7165,17 +7165,17 @@
       <c r="S20" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="11">
         <v>4</v>
       </c>
-      <c r="U20">
+      <c r="U20" s="11">
         <v>0</v>
       </c>
-      <c r="V20">
+      <c r="V20" s="11">
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7230,17 +7230,17 @@
       <c r="S21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-      <c r="U21">
+      <c r="T21" s="11">
+        <v>1</v>
+      </c>
+      <c r="U21" s="11">
         <v>0</v>
       </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V21" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7295,17 +7295,17 @@
       <c r="S22" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-      <c r="U22">
+      <c r="T22" s="11">
+        <v>1</v>
+      </c>
+      <c r="U22" s="11">
         <v>6</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="11">
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7360,17 +7360,17 @@
       <c r="S23" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
+      <c r="T23" s="11">
+        <v>1</v>
+      </c>
+      <c r="U23" s="11">
         <v>0</v>
       </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V23" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7425,17 +7425,17 @@
       <c r="S24" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
+      <c r="T24" s="11">
+        <v>1</v>
+      </c>
+      <c r="U24" s="11">
         <v>0</v>
       </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="V24" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7490,17 +7490,17 @@
       <c r="S25" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="T25">
+      <c r="T25" s="11">
         <v>0</v>
       </c>
-      <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U25" s="11">
+        <v>1</v>
+      </c>
+      <c r="V25" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7555,17 +7555,17 @@
       <c r="S26" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="T26">
+      <c r="T26" s="11">
         <v>0</v>
       </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U26" s="11">
+        <v>1</v>
+      </c>
+      <c r="V26" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7620,17 +7620,17 @@
       <c r="S27" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="T27">
+      <c r="T27" s="11">
         <v>235</v>
       </c>
-      <c r="U27">
+      <c r="U27" s="11">
         <v>273</v>
       </c>
-      <c r="V27">
+      <c r="V27" s="11">
         <v>508</v>
       </c>
     </row>
-    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7683,7 +7683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7738,13 +7738,13 @@
       <c r="R29" t="s">
         <v>47</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="S29" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="T29" s="12"/>
-      <c r="U29" s="12"/>
-    </row>
-    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7796,17 +7796,17 @@
       <c r="Q30">
         <v>1</v>
       </c>
-      <c r="S30" s="11" t="s">
+      <c r="S30" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="T30" s="13" t="s">
+      <c r="T30" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="U30" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U30" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -7858,15 +7858,15 @@
       <c r="Q31">
         <v>1</v>
       </c>
-      <c r="S31" s="11"/>
-      <c r="T31" s="13" t="s">
+      <c r="S31" s="12"/>
+      <c r="T31" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="U31" s="12">
+      <c r="U31" s="13">
         <v>0.998</v>
       </c>
     </row>
-    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -7918,17 +7918,17 @@
       <c r="Q32">
         <v>1</v>
       </c>
-      <c r="S32" s="11" t="s">
+      <c r="S32" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="T32" s="13" t="s">
+      <c r="T32" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="U32" s="12">
+      <c r="U32" s="13">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -7980,15 +7980,15 @@
       <c r="Q33">
         <v>1</v>
       </c>
-      <c r="S33" s="12"/>
-      <c r="T33" s="13" t="s">
+      <c r="S33" s="13"/>
+      <c r="T33" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="U33" s="12">
+      <c r="U33" s="13">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8040,15 +8040,15 @@
       <c r="Q34">
         <v>1</v>
       </c>
-      <c r="S34" s="11" t="s">
+      <c r="S34" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="T34" s="13" t="s">
+      <c r="T34" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="U34" s="14"/>
-    </row>
-    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U34" s="15"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8100,15 +8100,15 @@
       <c r="Q35">
         <v>1</v>
       </c>
-      <c r="S35" s="11" t="s">
+      <c r="S35" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="T35" s="12" t="s">
+      <c r="T35" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="U35" s="12"/>
-    </row>
-    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="U35" s="13"/>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8160,14 +8160,14 @@
       <c r="Q36">
         <v>1</v>
       </c>
-      <c r="S36" s="11" t="s">
+      <c r="S36" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="12"/>
-      <c r="U36" s="12"/>
-      <c r="V36" s="12"/>
-    </row>
-    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8538,7 +8538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8750,7 +8750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8803,7 +8803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -8856,7 +8856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -8909,7 +8909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -8962,7 +8962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9068,7 +9068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9121,7 +9121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9439,7 +9439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9651,7 +9651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9810,7 +9810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -9916,7 +9916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10128,7 +10128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10181,7 +10181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10287,7 +10287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10340,7 +10340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10446,7 +10446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10499,7 +10499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10817,7 +10817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -10979,7 +10979,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11197,7 +11197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11250,7 +11250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11624,7 +11624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11677,7 +11677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11836,7 +11836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -11942,7 +11942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12101,7 +12101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12260,7 +12260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12313,7 +12313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12366,7 +12366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12419,7 +12419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12525,7 +12525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12578,7 +12578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12737,7 +12737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12790,7 +12790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -12949,7 +12949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13055,7 +13055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13161,7 +13161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13267,7 +13267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13323,7 +13323,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13435,7 +13435,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13488,7 +13488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13541,7 +13541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13753,7 +13753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -13859,7 +13859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -13965,7 +13965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14018,7 +14018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14071,7 +14071,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14177,7 +14177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14230,7 +14230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14551,7 +14551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14816,7 +14816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14869,7 +14869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -14922,7 +14922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -14975,7 +14975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15134,7 +15134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15293,7 +15293,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15346,7 +15346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15452,7 +15452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15558,7 +15558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15614,7 +15614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15667,7 +15667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15720,7 +15720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15773,7 +15773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15826,7 +15826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -15932,7 +15932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16041,7 +16041,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16147,7 +16147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16200,7 +16200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16256,7 +16256,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16309,7 +16309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16362,7 +16362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16468,7 +16468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16521,7 +16521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16630,7 +16630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16683,7 +16683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16736,7 +16736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16789,7 +16789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16842,7 +16842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16895,7 +16895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -16951,7 +16951,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17060,7 +17060,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17166,7 +17166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17219,7 +17219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17378,7 +17378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17431,7 +17431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17484,7 +17484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17537,7 +17537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17590,7 +17590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17643,7 +17643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17696,7 +17696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17802,7 +17802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17858,7 +17858,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -17911,7 +17911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -17964,7 +17964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18123,7 +18123,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18229,7 +18229,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="226" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18282,7 +18282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18335,7 +18335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18388,7 +18388,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="229" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
         <v>18</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
         <v>18</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
         <v>18</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
         <v>18</v>
       </c>
@@ -18600,7 +18600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
         <v>18</v>
       </c>
@@ -18653,7 +18653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
         <v>18</v>
       </c>
@@ -18706,7 +18706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
         <v>18</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
         <v>18</v>
       </c>
@@ -18812,7 +18812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="s">
         <v>18</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:17" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
         <v>18</v>
       </c>
@@ -18919,13 +18919,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V238" xr:uid="{DCB8D8C8-861C-4C7D-AE0F-98369D6D1283}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="Harpacticoida spp."/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>